--- a/forms/app/group_session.xlsx
+++ b/forms/app/group_session.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20387"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20390"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D-tree\config-dtree-newrepo\config-dtree\forms\app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A047AF-511B-4125-82A4-6FE6E5054B5E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F41B313-72FD-4E6F-B882-39C34A6F83B8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="95">
   <si>
     <t>type</t>
   </si>
@@ -304,6 +304,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mkutano wa kikundi ulifanyika lini? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tafadhali chagua tarehe ya nyuma </t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1315,9 @@
       <c r="I20" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J20" s="9"/>
+      <c r="J20" s="9" t="s">
+        <v>94</v>
+      </c>
       <c r="K20" s="10"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
@@ -28977,7 +28982,7 @@
       </c>
       <c r="C2" s="13">
         <f ca="1">NOW()</f>
-        <v>44778.506182986108</v>
+        <v>44830.719573958333</v>
       </c>
       <c r="D2" s="10" t="s">
         <v>81</v>

--- a/forms/app/group_session.xlsx
+++ b/forms/app/group_session.xlsx
@@ -1,23 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20394"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\D-Tree\config-dtree\forms\app\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F961DC6E-2413-42AF-ACC3-2A1941EE8AE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7080" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" r:id="rId3"/>
+    <sheet state="visible" name="survey" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="choices" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="settings" sheetId="3" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataSignature="AMtx7mhU88ao7ZK8wdjL+y/4pxckfQrp+Q=="/>
@@ -27,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="97">
   <si>
     <t>type</t>
   </si>
@@ -323,35 +314,35 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dmmyyyyhm"/>
   </numFmts>
   <fonts count="5">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Sans"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Roboto"/>
     </font>
@@ -361,7 +352,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -371,58 +362,56 @@
     </fill>
   </fills>
   <borders count="2">
+    <border/>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -612,20 +601,20 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="26" width="18" customWidth="1"/>
+    <col customWidth="1" min="1" max="26" width="18.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -679,7 +668,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -717,16 +706,14 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -751,16 +738,14 @@
       <c r="Y3" s="3"/>
       <c r="Z3" s="3"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -785,16 +770,14 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -819,7 +802,7 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
@@ -855,7 +838,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -891,16 +874,14 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>74</v>
-      </c>
+      <c r="C8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -925,7 +906,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>30</v>
       </c>
@@ -961,7 +942,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
@@ -997,7 +978,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
@@ -1033,7 +1014,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>30</v>
       </c>
@@ -1069,7 +1050,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>37</v>
       </c>
@@ -1099,7 +1080,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
@@ -1129,7 +1110,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>22</v>
       </c>
@@ -1163,7 +1144,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1197,7 +1178,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>22</v>
       </c>
@@ -1231,7 +1212,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>22</v>
       </c>
@@ -1265,7 +1246,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26" ht="12.75" customHeight="1">
+    <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>41</v>
       </c>
@@ -1297,7 +1278,7 @@
       <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
     </row>
-    <row r="20" spans="1:26" ht="12.75" customHeight="1">
+    <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>42</v>
       </c>
@@ -1329,7 +1310,7 @@
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
     </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>13</v>
       </c>
@@ -1367,7 +1348,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>46</v>
       </c>
@@ -1411,7 +1392,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="12.75" customHeight="1">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>54</v>
       </c>
@@ -1448,7 +1429,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="12.75" customHeight="1">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="2" t="s">
         <v>54</v>
       </c>
@@ -1486,7 +1467,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="12.75" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>54</v>
       </c>
@@ -1524,7 +1505,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="12.75" customHeight="1">
+    <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="2" t="s">
         <v>37</v>
       </c>
@@ -1556,7 +1537,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="12.75" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1584,7 +1565,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="12.75" customHeight="1">
+    <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>13</v>
       </c>
@@ -1622,7 +1603,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" spans="1:26" ht="12.75" customHeight="1">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>68</v>
       </c>
@@ -1660,7 +1641,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" spans="1:26" ht="12.75" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>22</v>
       </c>
@@ -1698,7 +1679,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="12.75" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>68</v>
       </c>
@@ -1734,7 +1715,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" spans="1:26" ht="12.75" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>68</v>
       </c>
@@ -1772,7 +1753,7 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
-    <row r="33" spans="1:26" ht="12.75" customHeight="1">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>68</v>
       </c>
@@ -1808,7 +1789,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" spans="1:26" ht="12.75" customHeight="1">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>37</v>
       </c>
@@ -1840,7 +1821,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" spans="1:26" ht="12.75" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -1868,7 +1849,7 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
     </row>
-    <row r="36" spans="1:26" ht="12.75" customHeight="1">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -1896,7 +1877,7 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
     </row>
-    <row r="37" spans="1:26" ht="12.75" customHeight="1">
+    <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -1924,7 +1905,7 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
-    <row r="38" spans="1:26" ht="12.75" customHeight="1">
+    <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -1952,7 +1933,7 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
-    <row r="39" spans="1:26" ht="12.75" customHeight="1">
+    <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -1980,7 +1961,7 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
-    <row r="40" spans="1:26" ht="12.75" customHeight="1">
+    <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -2008,7 +1989,7 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
     </row>
-    <row r="41" spans="1:26" ht="12.75" customHeight="1">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -2036,7 +2017,7 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
     </row>
-    <row r="42" spans="1:26" ht="12.75" customHeight="1">
+    <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -2064,7 +2045,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" spans="1:26" ht="12.75" customHeight="1">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -2092,7 +2073,7 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44" spans="1:26" ht="12.75" customHeight="1">
+    <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -2120,7 +2101,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" spans="1:26" ht="12.75" customHeight="1">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -2148,7 +2129,7 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46" spans="1:26" ht="12.75" customHeight="1">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -2176,7 +2157,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" spans="1:26" ht="12.75" customHeight="1">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -2204,7 +2185,7 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
     </row>
-    <row r="48" spans="1:26" ht="12.75" customHeight="1">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -2232,7 +2213,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" spans="1:26" ht="12.75" customHeight="1">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -2260,7 +2241,7 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50" spans="1:26" ht="12.75" customHeight="1">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -2288,7 +2269,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" spans="1:26" ht="12.75" customHeight="1">
+    <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -2316,7 +2297,7 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
     </row>
-    <row r="52" spans="1:26" ht="12.75" customHeight="1">
+    <row r="52" ht="12.75" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -2344,7 +2325,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" spans="1:26" ht="12.75" customHeight="1">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -2372,7 +2353,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54" spans="1:26" ht="12.75" customHeight="1">
+    <row r="54" ht="12.75" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -2400,7 +2381,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" spans="1:26" ht="12.75" customHeight="1">
+    <row r="55" ht="12.75" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2428,7 +2409,7 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56" spans="1:26" ht="12.75" customHeight="1">
+    <row r="56" ht="12.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -2456,7 +2437,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57" spans="1:26" ht="12.75" customHeight="1">
+    <row r="57" ht="12.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -2484,7 +2465,7 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
     </row>
-    <row r="58" spans="1:26" ht="12.75" customHeight="1">
+    <row r="58" ht="12.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2512,7 +2493,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" spans="1:26" ht="12.75" customHeight="1">
+    <row r="59" ht="12.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2540,7 +2521,7 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60" spans="1:26" ht="12.75" customHeight="1">
+    <row r="60" ht="12.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -2568,7 +2549,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" spans="1:26" ht="12.75" customHeight="1">
+    <row r="61" ht="12.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -2596,7 +2577,7 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62" spans="1:26" ht="12.75" customHeight="1">
+    <row r="62" ht="12.75" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -2624,7 +2605,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" spans="1:26" ht="12.75" customHeight="1">
+    <row r="63" ht="12.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -2652,7 +2633,7 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64" spans="1:26" ht="12.75" customHeight="1">
+    <row r="64" ht="12.75" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -2680,7 +2661,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="1:26" ht="12.75" customHeight="1">
+    <row r="65" ht="12.75" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -2708,7 +2689,7 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66" spans="1:26" ht="12.75" customHeight="1">
+    <row r="66" ht="12.75" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -2736,7 +2717,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" spans="1:26" ht="12.75" customHeight="1">
+    <row r="67" ht="12.75" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -2764,7 +2745,7 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" spans="1:26" ht="12.75" customHeight="1">
+    <row r="68" ht="12.75" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -2792,7 +2773,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" spans="1:26" ht="12.75" customHeight="1">
+    <row r="69" ht="12.75" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -2820,7 +2801,7 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" spans="1:26" ht="12.75" customHeight="1">
+    <row r="70" ht="12.75" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -2848,7 +2829,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" spans="1:26" ht="12.75" customHeight="1">
+    <row r="71" ht="12.75" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -2876,7 +2857,7 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" spans="1:26" ht="12.75" customHeight="1">
+    <row r="72" ht="12.75" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -2904,7 +2885,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" spans="1:26" ht="12.75" customHeight="1">
+    <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -2932,7 +2913,7 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" spans="1:26" ht="12.75" customHeight="1">
+    <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -2960,7 +2941,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="1:26" ht="12.75" customHeight="1">
+    <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -2988,7 +2969,7 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" spans="1:26" ht="12.75" customHeight="1">
+    <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -3016,7 +2997,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="1:26" ht="12.75" customHeight="1">
+    <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -3044,7 +3025,7 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" spans="1:26" ht="12.75" customHeight="1">
+    <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -3072,7 +3053,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="1:26" ht="12.75" customHeight="1">
+    <row r="79" ht="12.75" customHeight="1">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -3100,7 +3081,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" spans="1:26" ht="12.75" customHeight="1">
+    <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3128,7 +3109,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" spans="1:26" ht="12.75" customHeight="1">
+    <row r="81" ht="12.75" customHeight="1">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -3156,7 +3137,7 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" spans="1:26" ht="12.75" customHeight="1">
+    <row r="82" ht="12.75" customHeight="1">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -3184,7 +3165,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="1:26" ht="12.75" customHeight="1">
+    <row r="83" ht="12.75" customHeight="1">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -3212,7 +3193,7 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84" spans="1:26" ht="12.75" customHeight="1">
+    <row r="84" ht="12.75" customHeight="1">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -3240,7 +3221,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" spans="1:26" ht="12.75" customHeight="1">
+    <row r="85" ht="12.75" customHeight="1">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -3268,7 +3249,7 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86" spans="1:26" ht="12.75" customHeight="1">
+    <row r="86" ht="12.75" customHeight="1">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -3296,7 +3277,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" spans="1:26" ht="12.75" customHeight="1">
+    <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -3324,7 +3305,7 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88" spans="1:26" ht="12.75" customHeight="1">
+    <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -3352,7 +3333,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" spans="1:26" ht="12.75" customHeight="1">
+    <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -3380,7 +3361,7 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
     </row>
-    <row r="90" spans="1:26" ht="12.75" customHeight="1">
+    <row r="90" ht="12.75" customHeight="1">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -3408,7 +3389,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" spans="1:26" ht="12.75" customHeight="1">
+    <row r="91" ht="12.75" customHeight="1">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -3436,7 +3417,7 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
     </row>
-    <row r="92" spans="1:26" ht="12.75" customHeight="1">
+    <row r="92" ht="12.75" customHeight="1">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -3464,7 +3445,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" spans="1:26" ht="12.75" customHeight="1">
+    <row r="93" ht="12.75" customHeight="1">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -3492,7 +3473,7 @@
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
     </row>
-    <row r="94" spans="1:26" ht="12.75" customHeight="1">
+    <row r="94" ht="12.75" customHeight="1">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -3520,7 +3501,7 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" spans="1:26" ht="12.75" customHeight="1">
+    <row r="95" ht="12.75" customHeight="1">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -3548,7 +3529,7 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" spans="1:26" ht="12.75" customHeight="1">
+    <row r="96" ht="12.75" customHeight="1">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -3576,7 +3557,7 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" spans="1:26" ht="12.75" customHeight="1">
+    <row r="97" ht="12.75" customHeight="1">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -3604,7 +3585,7 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" spans="1:26" ht="12.75" customHeight="1">
+    <row r="98" ht="12.75" customHeight="1">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -3632,7 +3613,7 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" spans="1:26" ht="12.75" customHeight="1">
+    <row r="99" ht="12.75" customHeight="1">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -3660,7 +3641,7 @@
       <c r="Y99" s="2"/>
       <c r="Z99" s="2"/>
     </row>
-    <row r="100" spans="1:26" ht="12.75" customHeight="1">
+    <row r="100" ht="12.75" customHeight="1">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -3688,7 +3669,7 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" spans="1:26" ht="12.75" customHeight="1">
+    <row r="101" ht="12.75" customHeight="1">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -3716,7 +3697,7 @@
       <c r="Y101" s="2"/>
       <c r="Z101" s="2"/>
     </row>
-    <row r="102" spans="1:26" ht="12.75" customHeight="1">
+    <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -3744,7 +3725,7 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" spans="1:26" ht="12.75" customHeight="1">
+    <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -3772,7 +3753,7 @@
       <c r="Y103" s="2"/>
       <c r="Z103" s="2"/>
     </row>
-    <row r="104" spans="1:26" ht="12.75" customHeight="1">
+    <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -3800,7 +3781,7 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
-    <row r="105" spans="1:26" ht="12.75" customHeight="1">
+    <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -3828,7 +3809,7 @@
       <c r="Y105" s="2"/>
       <c r="Z105" s="2"/>
     </row>
-    <row r="106" spans="1:26" ht="12.75" customHeight="1">
+    <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -3856,7 +3837,7 @@
       <c r="Y106" s="2"/>
       <c r="Z106" s="2"/>
     </row>
-    <row r="107" spans="1:26" ht="12.75" customHeight="1">
+    <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -3884,7 +3865,7 @@
       <c r="Y107" s="2"/>
       <c r="Z107" s="2"/>
     </row>
-    <row r="108" spans="1:26" ht="12.75" customHeight="1">
+    <row r="108" ht="12.75" customHeight="1">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -3912,7 +3893,7 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" spans="1:26" ht="12.75" customHeight="1">
+    <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -3940,7 +3921,7 @@
       <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
     </row>
-    <row r="110" spans="1:26" ht="12.75" customHeight="1">
+    <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -3968,7 +3949,7 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
-    <row r="111" spans="1:26" ht="12.75" customHeight="1">
+    <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -3996,7 +3977,7 @@
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
     </row>
-    <row r="112" spans="1:26" ht="12.75" customHeight="1">
+    <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -4024,7 +4005,7 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
     </row>
-    <row r="113" spans="1:26" ht="12.75" customHeight="1">
+    <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -4052,7 +4033,7 @@
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
     </row>
-    <row r="114" spans="1:26" ht="12.75" customHeight="1">
+    <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -4080,7 +4061,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115" spans="1:26" ht="12.75" customHeight="1">
+    <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -4108,7 +4089,7 @@
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
     </row>
-    <row r="116" spans="1:26" ht="12.75" customHeight="1">
+    <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -4136,7 +4117,7 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117" spans="1:26" ht="12.75" customHeight="1">
+    <row r="117" ht="12.75" customHeight="1">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -4164,7 +4145,7 @@
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
     </row>
-    <row r="118" spans="1:26" ht="12.75" customHeight="1">
+    <row r="118" ht="12.75" customHeight="1">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -4192,7 +4173,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119" spans="1:26" ht="12.75" customHeight="1">
+    <row r="119" ht="12.75" customHeight="1">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -4220,7 +4201,7 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
     </row>
-    <row r="120" spans="1:26" ht="12.75" customHeight="1">
+    <row r="120" ht="12.75" customHeight="1">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -4248,7 +4229,7 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121" spans="1:26" ht="12.75" customHeight="1">
+    <row r="121" ht="12.75" customHeight="1">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -4276,7 +4257,7 @@
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
     </row>
-    <row r="122" spans="1:26" ht="12.75" customHeight="1">
+    <row r="122" ht="12.75" customHeight="1">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -4304,7 +4285,7 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123" spans="1:26" ht="12.75" customHeight="1">
+    <row r="123" ht="12.75" customHeight="1">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -4332,7 +4313,7 @@
       <c r="Y123" s="2"/>
       <c r="Z123" s="2"/>
     </row>
-    <row r="124" spans="1:26" ht="12.75" customHeight="1">
+    <row r="124" ht="12.75" customHeight="1">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -4360,7 +4341,7 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125" spans="1:26" ht="12.75" customHeight="1">
+    <row r="125" ht="12.75" customHeight="1">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -4388,7 +4369,7 @@
       <c r="Y125" s="2"/>
       <c r="Z125" s="2"/>
     </row>
-    <row r="126" spans="1:26" ht="12.75" customHeight="1">
+    <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -4416,7 +4397,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127" spans="1:26" ht="12.75" customHeight="1">
+    <row r="127" ht="12.75" customHeight="1">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -4444,7 +4425,7 @@
       <c r="Y127" s="2"/>
       <c r="Z127" s="2"/>
     </row>
-    <row r="128" spans="1:26" ht="12.75" customHeight="1">
+    <row r="128" ht="12.75" customHeight="1">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -4472,7 +4453,7 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129" spans="1:26" ht="12.75" customHeight="1">
+    <row r="129" ht="12.75" customHeight="1">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -4500,7 +4481,7 @@
       <c r="Y129" s="2"/>
       <c r="Z129" s="2"/>
     </row>
-    <row r="130" spans="1:26" ht="12.75" customHeight="1">
+    <row r="130" ht="12.75" customHeight="1">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -4528,7 +4509,7 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
     </row>
-    <row r="131" spans="1:26" ht="12.75" customHeight="1">
+    <row r="131" ht="12.75" customHeight="1">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -4556,7 +4537,7 @@
       <c r="Y131" s="2"/>
       <c r="Z131" s="2"/>
     </row>
-    <row r="132" spans="1:26" ht="12.75" customHeight="1">
+    <row r="132" ht="12.75" customHeight="1">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -4584,7 +4565,7 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
     </row>
-    <row r="133" spans="1:26" ht="12.75" customHeight="1">
+    <row r="133" ht="12.75" customHeight="1">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -4612,7 +4593,7 @@
       <c r="Y133" s="2"/>
       <c r="Z133" s="2"/>
     </row>
-    <row r="134" spans="1:26" ht="12.75" customHeight="1">
+    <row r="134" ht="12.75" customHeight="1">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -4640,7 +4621,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" spans="1:26" ht="12.75" customHeight="1">
+    <row r="135" ht="12.75" customHeight="1">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -4668,7 +4649,7 @@
       <c r="Y135" s="2"/>
       <c r="Z135" s="2"/>
     </row>
-    <row r="136" spans="1:26" ht="12.75" customHeight="1">
+    <row r="136" ht="12.75" customHeight="1">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -4696,7 +4677,7 @@
       <c r="Y136" s="2"/>
       <c r="Z136" s="2"/>
     </row>
-    <row r="137" spans="1:26" ht="12.75" customHeight="1">
+    <row r="137" ht="12.75" customHeight="1">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -4724,7 +4705,7 @@
       <c r="Y137" s="2"/>
       <c r="Z137" s="2"/>
     </row>
-    <row r="138" spans="1:26" ht="12.75" customHeight="1">
+    <row r="138" ht="12.75" customHeight="1">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -4752,7 +4733,7 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
     </row>
-    <row r="139" spans="1:26" ht="12.75" customHeight="1">
+    <row r="139" ht="12.75" customHeight="1">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -4780,7 +4761,7 @@
       <c r="Y139" s="2"/>
       <c r="Z139" s="2"/>
     </row>
-    <row r="140" spans="1:26" ht="12.75" customHeight="1">
+    <row r="140" ht="12.75" customHeight="1">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -4808,7 +4789,7 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
     </row>
-    <row r="141" spans="1:26" ht="12.75" customHeight="1">
+    <row r="141" ht="12.75" customHeight="1">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -4836,7 +4817,7 @@
       <c r="Y141" s="2"/>
       <c r="Z141" s="2"/>
     </row>
-    <row r="142" spans="1:26" ht="12.75" customHeight="1">
+    <row r="142" ht="12.75" customHeight="1">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -4864,7 +4845,7 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
     </row>
-    <row r="143" spans="1:26" ht="12.75" customHeight="1">
+    <row r="143" ht="12.75" customHeight="1">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -4892,7 +4873,7 @@
       <c r="Y143" s="2"/>
       <c r="Z143" s="2"/>
     </row>
-    <row r="144" spans="1:26" ht="12.75" customHeight="1">
+    <row r="144" ht="12.75" customHeight="1">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -4920,7 +4901,7 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
     </row>
-    <row r="145" spans="1:26" ht="12.75" customHeight="1">
+    <row r="145" ht="12.75" customHeight="1">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -4948,7 +4929,7 @@
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
     </row>
-    <row r="146" spans="1:26" ht="12.75" customHeight="1">
+    <row r="146" ht="12.75" customHeight="1">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -4976,7 +4957,7 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147" spans="1:26" ht="12.75" customHeight="1">
+    <row r="147" ht="12.75" customHeight="1">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -5004,7 +4985,7 @@
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
     </row>
-    <row r="148" spans="1:26" ht="12.75" customHeight="1">
+    <row r="148" ht="12.75" customHeight="1">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -5032,7 +5013,7 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149" spans="1:26" ht="12.75" customHeight="1">
+    <row r="149" ht="12.75" customHeight="1">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -5060,7 +5041,7 @@
       <c r="Y149" s="2"/>
       <c r="Z149" s="2"/>
     </row>
-    <row r="150" spans="1:26" ht="12.75" customHeight="1">
+    <row r="150" ht="12.75" customHeight="1">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -5088,7 +5069,7 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
     </row>
-    <row r="151" spans="1:26" ht="12.75" customHeight="1">
+    <row r="151" ht="12.75" customHeight="1">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -5116,7 +5097,7 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152" spans="1:26" ht="12.75" customHeight="1">
+    <row r="152" ht="12.75" customHeight="1">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -5144,7 +5125,7 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
     </row>
-    <row r="153" spans="1:26" ht="12.75" customHeight="1">
+    <row r="153" ht="12.75" customHeight="1">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -5172,7 +5153,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154" spans="1:26" ht="12.75" customHeight="1">
+    <row r="154" ht="12.75" customHeight="1">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -5200,7 +5181,7 @@
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
     </row>
-    <row r="155" spans="1:26" ht="12.75" customHeight="1">
+    <row r="155" ht="12.75" customHeight="1">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -5228,7 +5209,7 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
     </row>
-    <row r="156" spans="1:26" ht="12.75" customHeight="1">
+    <row r="156" ht="12.75" customHeight="1">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -5256,7 +5237,7 @@
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
     </row>
-    <row r="157" spans="1:26" ht="12.75" customHeight="1">
+    <row r="157" ht="12.75" customHeight="1">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -5284,7 +5265,7 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158" spans="1:26" ht="12.75" customHeight="1">
+    <row r="158" ht="12.75" customHeight="1">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -5312,7 +5293,7 @@
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
     </row>
-    <row r="159" spans="1:26" ht="12.75" customHeight="1">
+    <row r="159" ht="12.75" customHeight="1">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -5340,7 +5321,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160" spans="1:26" ht="12.75" customHeight="1">
+    <row r="160" ht="12.75" customHeight="1">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -5368,7 +5349,7 @@
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
     </row>
-    <row r="161" spans="1:26" ht="12.75" customHeight="1">
+    <row r="161" ht="12.75" customHeight="1">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -5396,7 +5377,7 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
     </row>
-    <row r="162" spans="1:26" ht="12.75" customHeight="1">
+    <row r="162" ht="12.75" customHeight="1">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -5424,7 +5405,7 @@
       <c r="Y162" s="2"/>
       <c r="Z162" s="2"/>
     </row>
-    <row r="163" spans="1:26" ht="12.75" customHeight="1">
+    <row r="163" ht="12.75" customHeight="1">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -5452,7 +5433,7 @@
       <c r="Y163" s="2"/>
       <c r="Z163" s="2"/>
     </row>
-    <row r="164" spans="1:26" ht="12.75" customHeight="1">
+    <row r="164" ht="12.75" customHeight="1">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -5480,7 +5461,7 @@
       <c r="Y164" s="2"/>
       <c r="Z164" s="2"/>
     </row>
-    <row r="165" spans="1:26" ht="12.75" customHeight="1">
+    <row r="165" ht="12.75" customHeight="1">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -5508,7 +5489,7 @@
       <c r="Y165" s="2"/>
       <c r="Z165" s="2"/>
     </row>
-    <row r="166" spans="1:26" ht="12.75" customHeight="1">
+    <row r="166" ht="12.75" customHeight="1">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -5536,7 +5517,7 @@
       <c r="Y166" s="2"/>
       <c r="Z166" s="2"/>
     </row>
-    <row r="167" spans="1:26" ht="12.75" customHeight="1">
+    <row r="167" ht="12.75" customHeight="1">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -5564,7 +5545,7 @@
       <c r="Y167" s="2"/>
       <c r="Z167" s="2"/>
     </row>
-    <row r="168" spans="1:26" ht="12.75" customHeight="1">
+    <row r="168" ht="12.75" customHeight="1">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -5592,7 +5573,7 @@
       <c r="Y168" s="2"/>
       <c r="Z168" s="2"/>
     </row>
-    <row r="169" spans="1:26" ht="12.75" customHeight="1">
+    <row r="169" ht="12.75" customHeight="1">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -5620,7 +5601,7 @@
       <c r="Y169" s="2"/>
       <c r="Z169" s="2"/>
     </row>
-    <row r="170" spans="1:26" ht="12.75" customHeight="1">
+    <row r="170" ht="12.75" customHeight="1">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -5648,7 +5629,7 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
     </row>
-    <row r="171" spans="1:26" ht="12.75" customHeight="1">
+    <row r="171" ht="12.75" customHeight="1">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -5676,7 +5657,7 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
     </row>
-    <row r="172" spans="1:26" ht="12.75" customHeight="1">
+    <row r="172" ht="12.75" customHeight="1">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -5704,7 +5685,7 @@
       <c r="Y172" s="2"/>
       <c r="Z172" s="2"/>
     </row>
-    <row r="173" spans="1:26" ht="12.75" customHeight="1">
+    <row r="173" ht="12.75" customHeight="1">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -5732,7 +5713,7 @@
       <c r="Y173" s="2"/>
       <c r="Z173" s="2"/>
     </row>
-    <row r="174" spans="1:26" ht="12.75" customHeight="1">
+    <row r="174" ht="12.75" customHeight="1">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -5760,7 +5741,7 @@
       <c r="Y174" s="2"/>
       <c r="Z174" s="2"/>
     </row>
-    <row r="175" spans="1:26" ht="12.75" customHeight="1">
+    <row r="175" ht="12.75" customHeight="1">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -5788,7 +5769,7 @@
       <c r="Y175" s="2"/>
       <c r="Z175" s="2"/>
     </row>
-    <row r="176" spans="1:26" ht="12.75" customHeight="1">
+    <row r="176" ht="12.75" customHeight="1">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -5816,7 +5797,7 @@
       <c r="Y176" s="2"/>
       <c r="Z176" s="2"/>
     </row>
-    <row r="177" spans="1:26" ht="12.75" customHeight="1">
+    <row r="177" ht="12.75" customHeight="1">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -5844,7 +5825,7 @@
       <c r="Y177" s="2"/>
       <c r="Z177" s="2"/>
     </row>
-    <row r="178" spans="1:26" ht="12.75" customHeight="1">
+    <row r="178" ht="12.75" customHeight="1">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -5872,7 +5853,7 @@
       <c r="Y178" s="2"/>
       <c r="Z178" s="2"/>
     </row>
-    <row r="179" spans="1:26" ht="12.75" customHeight="1">
+    <row r="179" ht="12.75" customHeight="1">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -5900,7 +5881,7 @@
       <c r="Y179" s="2"/>
       <c r="Z179" s="2"/>
     </row>
-    <row r="180" spans="1:26" ht="12.75" customHeight="1">
+    <row r="180" ht="12.75" customHeight="1">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -5928,7 +5909,7 @@
       <c r="Y180" s="2"/>
       <c r="Z180" s="2"/>
     </row>
-    <row r="181" spans="1:26" ht="12.75" customHeight="1">
+    <row r="181" ht="12.75" customHeight="1">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -5956,7 +5937,7 @@
       <c r="Y181" s="2"/>
       <c r="Z181" s="2"/>
     </row>
-    <row r="182" spans="1:26" ht="12.75" customHeight="1">
+    <row r="182" ht="12.75" customHeight="1">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -5984,7 +5965,7 @@
       <c r="Y182" s="2"/>
       <c r="Z182" s="2"/>
     </row>
-    <row r="183" spans="1:26" ht="12.75" customHeight="1">
+    <row r="183" ht="12.75" customHeight="1">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -6012,7 +5993,7 @@
       <c r="Y183" s="2"/>
       <c r="Z183" s="2"/>
     </row>
-    <row r="184" spans="1:26" ht="12.75" customHeight="1">
+    <row r="184" ht="12.75" customHeight="1">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -6040,7 +6021,7 @@
       <c r="Y184" s="2"/>
       <c r="Z184" s="2"/>
     </row>
-    <row r="185" spans="1:26" ht="12.75" customHeight="1">
+    <row r="185" ht="12.75" customHeight="1">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -6068,7 +6049,7 @@
       <c r="Y185" s="2"/>
       <c r="Z185" s="2"/>
     </row>
-    <row r="186" spans="1:26" ht="12.75" customHeight="1">
+    <row r="186" ht="12.75" customHeight="1">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -6096,7 +6077,7 @@
       <c r="Y186" s="2"/>
       <c r="Z186" s="2"/>
     </row>
-    <row r="187" spans="1:26" ht="12.75" customHeight="1">
+    <row r="187" ht="12.75" customHeight="1">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -6124,7 +6105,7 @@
       <c r="Y187" s="2"/>
       <c r="Z187" s="2"/>
     </row>
-    <row r="188" spans="1:26" ht="12.75" customHeight="1">
+    <row r="188" ht="12.75" customHeight="1">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -6152,7 +6133,7 @@
       <c r="Y188" s="2"/>
       <c r="Z188" s="2"/>
     </row>
-    <row r="189" spans="1:26" ht="12.75" customHeight="1">
+    <row r="189" ht="12.75" customHeight="1">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -6180,7 +6161,7 @@
       <c r="Y189" s="2"/>
       <c r="Z189" s="2"/>
     </row>
-    <row r="190" spans="1:26" ht="12.75" customHeight="1">
+    <row r="190" ht="12.75" customHeight="1">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -6208,7 +6189,7 @@
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
     </row>
-    <row r="191" spans="1:26" ht="12.75" customHeight="1">
+    <row r="191" ht="12.75" customHeight="1">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -6236,7 +6217,7 @@
       <c r="Y191" s="2"/>
       <c r="Z191" s="2"/>
     </row>
-    <row r="192" spans="1:26" ht="12.75" customHeight="1">
+    <row r="192" ht="12.75" customHeight="1">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -6264,7 +6245,7 @@
       <c r="Y192" s="2"/>
       <c r="Z192" s="2"/>
     </row>
-    <row r="193" spans="1:26" ht="12.75" customHeight="1">
+    <row r="193" ht="12.75" customHeight="1">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -6292,7 +6273,7 @@
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
     </row>
-    <row r="194" spans="1:26" ht="12.75" customHeight="1">
+    <row r="194" ht="12.75" customHeight="1">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -6320,7 +6301,7 @@
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
     </row>
-    <row r="195" spans="1:26" ht="12.75" customHeight="1">
+    <row r="195" ht="12.75" customHeight="1">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -6348,7 +6329,7 @@
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
     </row>
-    <row r="196" spans="1:26" ht="12.75" customHeight="1">
+    <row r="196" ht="12.75" customHeight="1">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -6376,7 +6357,7 @@
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
     </row>
-    <row r="197" spans="1:26" ht="12.75" customHeight="1">
+    <row r="197" ht="12.75" customHeight="1">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -6404,7 +6385,7 @@
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
     </row>
-    <row r="198" spans="1:26" ht="12.75" customHeight="1">
+    <row r="198" ht="12.75" customHeight="1">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -6432,7 +6413,7 @@
       <c r="Y198" s="2"/>
       <c r="Z198" s="2"/>
     </row>
-    <row r="199" spans="1:26" ht="12.75" customHeight="1">
+    <row r="199" ht="12.75" customHeight="1">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -6460,7 +6441,7 @@
       <c r="Y199" s="2"/>
       <c r="Z199" s="2"/>
     </row>
-    <row r="200" spans="1:26" ht="12.75" customHeight="1">
+    <row r="200" ht="12.75" customHeight="1">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -6488,7 +6469,7 @@
       <c r="Y200" s="2"/>
       <c r="Z200" s="2"/>
     </row>
-    <row r="201" spans="1:26" ht="12.75" customHeight="1">
+    <row r="201" ht="12.75" customHeight="1">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -6516,7 +6497,7 @@
       <c r="Y201" s="2"/>
       <c r="Z201" s="2"/>
     </row>
-    <row r="202" spans="1:26" ht="12.75" customHeight="1">
+    <row r="202" ht="12.75" customHeight="1">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -6544,7 +6525,7 @@
       <c r="Y202" s="2"/>
       <c r="Z202" s="2"/>
     </row>
-    <row r="203" spans="1:26" ht="12.75" customHeight="1">
+    <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -6572,7 +6553,7 @@
       <c r="Y203" s="2"/>
       <c r="Z203" s="2"/>
     </row>
-    <row r="204" spans="1:26" ht="12.75" customHeight="1">
+    <row r="204" ht="12.75" customHeight="1">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -6600,7 +6581,7 @@
       <c r="Y204" s="2"/>
       <c r="Z204" s="2"/>
     </row>
-    <row r="205" spans="1:26" ht="12.75" customHeight="1">
+    <row r="205" ht="12.75" customHeight="1">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -6628,7 +6609,7 @@
       <c r="Y205" s="2"/>
       <c r="Z205" s="2"/>
     </row>
-    <row r="206" spans="1:26" ht="12.75" customHeight="1">
+    <row r="206" ht="12.75" customHeight="1">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -6656,7 +6637,7 @@
       <c r="Y206" s="2"/>
       <c r="Z206" s="2"/>
     </row>
-    <row r="207" spans="1:26" ht="12.75" customHeight="1">
+    <row r="207" ht="12.75" customHeight="1">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -6684,7 +6665,7 @@
       <c r="Y207" s="2"/>
       <c r="Z207" s="2"/>
     </row>
-    <row r="208" spans="1:26" ht="12.75" customHeight="1">
+    <row r="208" ht="12.75" customHeight="1">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -6712,7 +6693,7 @@
       <c r="Y208" s="2"/>
       <c r="Z208" s="2"/>
     </row>
-    <row r="209" spans="1:26" ht="12.75" customHeight="1">
+    <row r="209" ht="12.75" customHeight="1">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -6740,7 +6721,7 @@
       <c r="Y209" s="2"/>
       <c r="Z209" s="2"/>
     </row>
-    <row r="210" spans="1:26" ht="12.75" customHeight="1">
+    <row r="210" ht="12.75" customHeight="1">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -6768,7 +6749,7 @@
       <c r="Y210" s="2"/>
       <c r="Z210" s="2"/>
     </row>
-    <row r="211" spans="1:26" ht="12.75" customHeight="1">
+    <row r="211" ht="12.75" customHeight="1">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -6796,7 +6777,7 @@
       <c r="Y211" s="2"/>
       <c r="Z211" s="2"/>
     </row>
-    <row r="212" spans="1:26" ht="12.75" customHeight="1">
+    <row r="212" ht="12.75" customHeight="1">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -6824,7 +6805,7 @@
       <c r="Y212" s="2"/>
       <c r="Z212" s="2"/>
     </row>
-    <row r="213" spans="1:26" ht="12.75" customHeight="1">
+    <row r="213" ht="12.75" customHeight="1">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -6852,7 +6833,7 @@
       <c r="Y213" s="2"/>
       <c r="Z213" s="2"/>
     </row>
-    <row r="214" spans="1:26" ht="12.75" customHeight="1">
+    <row r="214" ht="12.75" customHeight="1">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -6880,7 +6861,7 @@
       <c r="Y214" s="2"/>
       <c r="Z214" s="2"/>
     </row>
-    <row r="215" spans="1:26" ht="12.75" customHeight="1">
+    <row r="215" ht="12.75" customHeight="1">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -6908,7 +6889,7 @@
       <c r="Y215" s="2"/>
       <c r="Z215" s="2"/>
     </row>
-    <row r="216" spans="1:26" ht="12.75" customHeight="1">
+    <row r="216" ht="12.75" customHeight="1">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -6936,7 +6917,7 @@
       <c r="Y216" s="2"/>
       <c r="Z216" s="2"/>
     </row>
-    <row r="217" spans="1:26" ht="12.75" customHeight="1">
+    <row r="217" ht="12.75" customHeight="1">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -6964,7 +6945,7 @@
       <c r="Y217" s="2"/>
       <c r="Z217" s="2"/>
     </row>
-    <row r="218" spans="1:26" ht="12.75" customHeight="1">
+    <row r="218" ht="12.75" customHeight="1">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -6992,7 +6973,7 @@
       <c r="Y218" s="2"/>
       <c r="Z218" s="2"/>
     </row>
-    <row r="219" spans="1:26" ht="12.75" customHeight="1">
+    <row r="219" ht="12.75" customHeight="1">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -7020,7 +7001,7 @@
       <c r="Y219" s="2"/>
       <c r="Z219" s="2"/>
     </row>
-    <row r="220" spans="1:26" ht="12.75" customHeight="1">
+    <row r="220" ht="12.75" customHeight="1">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -7048,7 +7029,7 @@
       <c r="Y220" s="2"/>
       <c r="Z220" s="2"/>
     </row>
-    <row r="221" spans="1:26" ht="12.75" customHeight="1">
+    <row r="221" ht="12.75" customHeight="1">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -7076,7 +7057,7 @@
       <c r="Y221" s="2"/>
       <c r="Z221" s="2"/>
     </row>
-    <row r="222" spans="1:26" ht="12.75" customHeight="1">
+    <row r="222" ht="12.75" customHeight="1">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -7104,7 +7085,7 @@
       <c r="Y222" s="2"/>
       <c r="Z222" s="2"/>
     </row>
-    <row r="223" spans="1:26" ht="12.75" customHeight="1">
+    <row r="223" ht="12.75" customHeight="1">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -7132,7 +7113,7 @@
       <c r="Y223" s="2"/>
       <c r="Z223" s="2"/>
     </row>
-    <row r="224" spans="1:26" ht="12.75" customHeight="1">
+    <row r="224" ht="12.75" customHeight="1">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -7160,7 +7141,7 @@
       <c r="Y224" s="2"/>
       <c r="Z224" s="2"/>
     </row>
-    <row r="225" spans="1:26" ht="12.75" customHeight="1">
+    <row r="225" ht="12.75" customHeight="1">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -7188,7 +7169,7 @@
       <c r="Y225" s="2"/>
       <c r="Z225" s="2"/>
     </row>
-    <row r="226" spans="1:26" ht="12.75" customHeight="1">
+    <row r="226" ht="12.75" customHeight="1">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -7216,7 +7197,7 @@
       <c r="Y226" s="2"/>
       <c r="Z226" s="2"/>
     </row>
-    <row r="227" spans="1:26" ht="12.75" customHeight="1">
+    <row r="227" ht="12.75" customHeight="1">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -7244,7 +7225,7 @@
       <c r="Y227" s="2"/>
       <c r="Z227" s="2"/>
     </row>
-    <row r="228" spans="1:26" ht="12.75" customHeight="1">
+    <row r="228" ht="12.75" customHeight="1">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -7272,7 +7253,7 @@
       <c r="Y228" s="2"/>
       <c r="Z228" s="2"/>
     </row>
-    <row r="229" spans="1:26" ht="12.75" customHeight="1">
+    <row r="229" ht="12.75" customHeight="1">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -7300,7 +7281,7 @@
       <c r="Y229" s="2"/>
       <c r="Z229" s="2"/>
     </row>
-    <row r="230" spans="1:26" ht="12.75" customHeight="1">
+    <row r="230" ht="12.75" customHeight="1">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -7328,7 +7309,7 @@
       <c r="Y230" s="2"/>
       <c r="Z230" s="2"/>
     </row>
-    <row r="231" spans="1:26" ht="12.75" customHeight="1">
+    <row r="231" ht="12.75" customHeight="1">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -7356,7 +7337,7 @@
       <c r="Y231" s="2"/>
       <c r="Z231" s="2"/>
     </row>
-    <row r="232" spans="1:26" ht="12.75" customHeight="1">
+    <row r="232" ht="12.75" customHeight="1">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -7384,7 +7365,7 @@
       <c r="Y232" s="2"/>
       <c r="Z232" s="2"/>
     </row>
-    <row r="233" spans="1:26" ht="12.75" customHeight="1">
+    <row r="233" ht="12.75" customHeight="1">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -7412,7 +7393,7 @@
       <c r="Y233" s="2"/>
       <c r="Z233" s="2"/>
     </row>
-    <row r="234" spans="1:26" ht="12.75" customHeight="1">
+    <row r="234" ht="12.75" customHeight="1">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -7440,12 +7421,12 @@
       <c r="Y234" s="2"/>
       <c r="Z234" s="2"/>
     </row>
-    <row r="235" spans="1:26" ht="12.75" customHeight="1"/>
-    <row r="236" spans="1:26" ht="12.75" customHeight="1"/>
-    <row r="237" spans="1:26" ht="12.75" customHeight="1"/>
-    <row r="238" spans="1:26" ht="12.75" customHeight="1"/>
-    <row r="239" spans="1:26" ht="12.75" customHeight="1"/>
-    <row r="240" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="235" ht="12.75" customHeight="1"/>
+    <row r="236" ht="12.75" customHeight="1"/>
+    <row r="237" ht="12.75" customHeight="1"/>
+    <row r="238" ht="12.75" customHeight="1"/>
+    <row r="239" ht="12.75" customHeight="1"/>
+    <row r="240" ht="12.75" customHeight="1"/>
     <row r="241" ht="12.75" customHeight="1"/>
     <row r="242" ht="12.75" customHeight="1"/>
     <row r="243" ht="12.75" customHeight="1"/>
@@ -8207,20 +8188,24 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:X1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="6" width="12.5703125" customWidth="1"/>
+    <col customWidth="1" min="1" max="6" width="12.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15.75" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>85</v>
       </c>
@@ -8254,21 +8239,21 @@
       <c r="W1" s="6"/>
       <c r="X1" s="6"/>
     </row>
-    <row r="2" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="3" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="4" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="5" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="6" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="7" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="8" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="9" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="10" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="11" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="12" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="13" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="14" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="15" spans="1:24" ht="12.75" customHeight="1"/>
-    <row r="16" spans="1:24" ht="12.75" customHeight="1"/>
+    <row r="2" ht="12.75" customHeight="1"/>
+    <row r="3" ht="12.75" customHeight="1"/>
+    <row r="4" ht="12.75" customHeight="1"/>
+    <row r="5" ht="12.75" customHeight="1"/>
+    <row r="6" ht="12.75" customHeight="1"/>
+    <row r="7" ht="12.75" customHeight="1"/>
+    <row r="8" ht="12.75" customHeight="1"/>
+    <row r="9" ht="12.75" customHeight="1"/>
+    <row r="10" ht="12.75" customHeight="1"/>
+    <row r="11" ht="12.75" customHeight="1"/>
+    <row r="12" ht="12.75" customHeight="1"/>
+    <row r="13" ht="12.75" customHeight="1"/>
+    <row r="14" ht="12.75" customHeight="1"/>
+    <row r="15" ht="12.75" customHeight="1"/>
+    <row r="16" ht="12.75" customHeight="1"/>
     <row r="17" ht="12.75" customHeight="1"/>
     <row r="18" ht="12.75" customHeight="1"/>
     <row r="19" ht="12.75" customHeight="1"/>
@@ -9254,20 +9239,24 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="26" width="17.42578125" customWidth="1"/>
+    <col customWidth="1" min="1" max="26" width="17.38"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="15.75" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
@@ -9307,7 +9296,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="15.75" customHeight="1">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>92</v>
       </c>
@@ -9315,8 +9304,8 @@
         <v>93</v>
       </c>
       <c r="C2" s="7">
-        <f ca="1">NOW()</f>
-        <v>44949.603663888891</v>
+        <f>NOW()</f>
+        <v>44949.10609</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>94</v>
@@ -9348,7 +9337,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="15.75" customHeight="1">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -9376,7 +9365,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="15.75" customHeight="1">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -9404,7 +9393,7 @@
       <c r="Y4" s="2"/>
       <c r="Z4" s="2"/>
     </row>
-    <row r="5" spans="1:26" ht="15.75" customHeight="1">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -9432,7 +9421,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="15.75" customHeight="1">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -9460,7 +9449,7 @@
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
     </row>
-    <row r="7" spans="1:26" ht="15.75" customHeight="1">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -9488,7 +9477,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="15.75" customHeight="1">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -9516,7 +9505,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="15.75" customHeight="1">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
@@ -9544,7 +9533,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="15.75" customHeight="1">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
@@ -9572,7 +9561,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="15.75" customHeight="1">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -9600,7 +9589,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="15.75" customHeight="1">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -9628,7 +9617,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="15.75" customHeight="1">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -9656,7 +9645,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="15.75" customHeight="1">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -9684,7 +9673,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="15.75" customHeight="1">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -9712,7 +9701,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="15.75" customHeight="1">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -9740,7 +9729,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
@@ -9768,7 +9757,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -9796,7 +9785,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="15.75" customHeight="1">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -9824,7 +9813,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="15.75" customHeight="1">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -9852,7 +9841,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="12.75" customHeight="1">
+    <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -9880,7 +9869,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="12.75" customHeight="1">
+    <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -9908,7 +9897,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="12.75" customHeight="1">
+    <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -9936,7 +9925,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="12.75" customHeight="1">
+    <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -9964,7 +9953,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="12.75" customHeight="1">
+    <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -9992,7 +9981,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="12.75" customHeight="1">
+    <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -10020,7 +10009,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="12.75" customHeight="1">
+    <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -10048,7 +10037,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="12.75" customHeight="1">
+    <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -10076,7 +10065,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="12.75" customHeight="1">
+    <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -10104,7 +10093,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="12.75" customHeight="1">
+    <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -10132,7 +10121,7 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
-    <row r="31" spans="1:26" ht="12.75" customHeight="1">
+    <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -10160,7 +10149,7 @@
       <c r="Y31" s="2"/>
       <c r="Z31" s="2"/>
     </row>
-    <row r="32" spans="1:26" ht="12.75" customHeight="1">
+    <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -10188,7 +10177,7 @@
       <c r="Y32" s="2"/>
       <c r="Z32" s="2"/>
     </row>
-    <row r="33" spans="1:26" ht="12.75" customHeight="1">
+    <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -10216,7 +10205,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" spans="1:26" ht="12.75" customHeight="1">
+    <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -10244,7 +10233,7 @@
       <c r="Y34" s="2"/>
       <c r="Z34" s="2"/>
     </row>
-    <row r="35" spans="1:26" ht="12.75" customHeight="1">
+    <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -10272,7 +10261,7 @@
       <c r="Y35" s="2"/>
       <c r="Z35" s="2"/>
     </row>
-    <row r="36" spans="1:26" ht="12.75" customHeight="1">
+    <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -10300,7 +10289,7 @@
       <c r="Y36" s="2"/>
       <c r="Z36" s="2"/>
     </row>
-    <row r="37" spans="1:26" ht="12.75" customHeight="1">
+    <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -10328,7 +10317,7 @@
       <c r="Y37" s="2"/>
       <c r="Z37" s="2"/>
     </row>
-    <row r="38" spans="1:26" ht="12.75" customHeight="1">
+    <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -10356,7 +10345,7 @@
       <c r="Y38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
-    <row r="39" spans="1:26" ht="12.75" customHeight="1">
+    <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -10384,7 +10373,7 @@
       <c r="Y39" s="2"/>
       <c r="Z39" s="2"/>
     </row>
-    <row r="40" spans="1:26" ht="12.75" customHeight="1">
+    <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -10412,7 +10401,7 @@
       <c r="Y40" s="2"/>
       <c r="Z40" s="2"/>
     </row>
-    <row r="41" spans="1:26" ht="12.75" customHeight="1">
+    <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -10440,7 +10429,7 @@
       <c r="Y41" s="2"/>
       <c r="Z41" s="2"/>
     </row>
-    <row r="42" spans="1:26" ht="12.75" customHeight="1">
+    <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -10468,7 +10457,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" spans="1:26" ht="12.75" customHeight="1">
+    <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -10496,7 +10485,7 @@
       <c r="Y43" s="2"/>
       <c r="Z43" s="2"/>
     </row>
-    <row r="44" spans="1:26" ht="12.75" customHeight="1">
+    <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -10524,7 +10513,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" spans="1:26" ht="12.75" customHeight="1">
+    <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -10552,7 +10541,7 @@
       <c r="Y45" s="2"/>
       <c r="Z45" s="2"/>
     </row>
-    <row r="46" spans="1:26" ht="12.75" customHeight="1">
+    <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -10580,7 +10569,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" spans="1:26" ht="12.75" customHeight="1">
+    <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -10608,7 +10597,7 @@
       <c r="Y47" s="2"/>
       <c r="Z47" s="2"/>
     </row>
-    <row r="48" spans="1:26" ht="12.75" customHeight="1">
+    <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -10636,7 +10625,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" spans="1:26" ht="12.75" customHeight="1">
+    <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -10664,7 +10653,7 @@
       <c r="Y49" s="2"/>
       <c r="Z49" s="2"/>
     </row>
-    <row r="50" spans="1:26" ht="12.75" customHeight="1">
+    <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -10692,7 +10681,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" spans="1:26" ht="12.75" customHeight="1">
+    <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -10720,7 +10709,7 @@
       <c r="Y51" s="2"/>
       <c r="Z51" s="2"/>
     </row>
-    <row r="52" spans="1:26" ht="12.75" customHeight="1">
+    <row r="52" ht="12.75" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -10748,7 +10737,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" spans="1:26" ht="12.75" customHeight="1">
+    <row r="53" ht="12.75" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -10776,7 +10765,7 @@
       <c r="Y53" s="2"/>
       <c r="Z53" s="2"/>
     </row>
-    <row r="54" spans="1:26" ht="12.75" customHeight="1">
+    <row r="54" ht="12.75" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -10804,7 +10793,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" spans="1:26" ht="12.75" customHeight="1">
+    <row r="55" ht="12.75" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -10832,7 +10821,7 @@
       <c r="Y55" s="2"/>
       <c r="Z55" s="2"/>
     </row>
-    <row r="56" spans="1:26" ht="12.75" customHeight="1">
+    <row r="56" ht="12.75" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -10860,7 +10849,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57" spans="1:26" ht="12.75" customHeight="1">
+    <row r="57" ht="12.75" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -10888,7 +10877,7 @@
       <c r="Y57" s="2"/>
       <c r="Z57" s="2"/>
     </row>
-    <row r="58" spans="1:26" ht="12.75" customHeight="1">
+    <row r="58" ht="12.75" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -10916,7 +10905,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" spans="1:26" ht="12.75" customHeight="1">
+    <row r="59" ht="12.75" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -10944,7 +10933,7 @@
       <c r="Y59" s="2"/>
       <c r="Z59" s="2"/>
     </row>
-    <row r="60" spans="1:26" ht="12.75" customHeight="1">
+    <row r="60" ht="12.75" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -10972,7 +10961,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" spans="1:26" ht="12.75" customHeight="1">
+    <row r="61" ht="12.75" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
@@ -11000,7 +10989,7 @@
       <c r="Y61" s="2"/>
       <c r="Z61" s="2"/>
     </row>
-    <row r="62" spans="1:26" ht="12.75" customHeight="1">
+    <row r="62" ht="12.75" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
@@ -11028,7 +11017,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" spans="1:26" ht="12.75" customHeight="1">
+    <row r="63" ht="12.75" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
@@ -11056,7 +11045,7 @@
       <c r="Y63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
-    <row r="64" spans="1:26" ht="12.75" customHeight="1">
+    <row r="64" ht="12.75" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -11084,7 +11073,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="1:26" ht="12.75" customHeight="1">
+    <row r="65" ht="12.75" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -11112,7 +11101,7 @@
       <c r="Y65" s="2"/>
       <c r="Z65" s="2"/>
     </row>
-    <row r="66" spans="1:26" ht="12.75" customHeight="1">
+    <row r="66" ht="12.75" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
@@ -11140,7 +11129,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" spans="1:26" ht="12.75" customHeight="1">
+    <row r="67" ht="12.75" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -11168,7 +11157,7 @@
       <c r="Y67" s="2"/>
       <c r="Z67" s="2"/>
     </row>
-    <row r="68" spans="1:26" ht="12.75" customHeight="1">
+    <row r="68" ht="12.75" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
@@ -11196,7 +11185,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" spans="1:26" ht="12.75" customHeight="1">
+    <row r="69" ht="12.75" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
@@ -11224,7 +11213,7 @@
       <c r="Y69" s="2"/>
       <c r="Z69" s="2"/>
     </row>
-    <row r="70" spans="1:26" ht="12.75" customHeight="1">
+    <row r="70" ht="12.75" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
@@ -11252,7 +11241,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" spans="1:26" ht="12.75" customHeight="1">
+    <row r="71" ht="12.75" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -11280,7 +11269,7 @@
       <c r="Y71" s="2"/>
       <c r="Z71" s="2"/>
     </row>
-    <row r="72" spans="1:26" ht="12.75" customHeight="1">
+    <row r="72" ht="12.75" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
@@ -11308,7 +11297,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" spans="1:26" ht="12.75" customHeight="1">
+    <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
@@ -11336,7 +11325,7 @@
       <c r="Y73" s="2"/>
       <c r="Z73" s="2"/>
     </row>
-    <row r="74" spans="1:26" ht="12.75" customHeight="1">
+    <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
@@ -11364,7 +11353,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="1:26" ht="12.75" customHeight="1">
+    <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -11392,7 +11381,7 @@
       <c r="Y75" s="2"/>
       <c r="Z75" s="2"/>
     </row>
-    <row r="76" spans="1:26" ht="12.75" customHeight="1">
+    <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -11420,7 +11409,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="1:26" ht="12.75" customHeight="1">
+    <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -11448,7 +11437,7 @@
       <c r="Y77" s="2"/>
       <c r="Z77" s="2"/>
     </row>
-    <row r="78" spans="1:26" ht="12.75" customHeight="1">
+    <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -11476,7 +11465,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="1:26" ht="12.75" customHeight="1">
+    <row r="79" ht="12.75" customHeight="1">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -11504,7 +11493,7 @@
       <c r="Y79" s="2"/>
       <c r="Z79" s="2"/>
     </row>
-    <row r="80" spans="1:26" ht="12.75" customHeight="1">
+    <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -11532,7 +11521,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" spans="1:26" ht="12.75" customHeight="1">
+    <row r="81" ht="12.75" customHeight="1">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -11560,7 +11549,7 @@
       <c r="Y81" s="2"/>
       <c r="Z81" s="2"/>
     </row>
-    <row r="82" spans="1:26" ht="12.75" customHeight="1">
+    <row r="82" ht="12.75" customHeight="1">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -11588,7 +11577,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="1:26" ht="12.75" customHeight="1">
+    <row r="83" ht="12.75" customHeight="1">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -11616,7 +11605,7 @@
       <c r="Y83" s="2"/>
       <c r="Z83" s="2"/>
     </row>
-    <row r="84" spans="1:26" ht="12.75" customHeight="1">
+    <row r="84" ht="12.75" customHeight="1">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -11644,7 +11633,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" spans="1:26" ht="12.75" customHeight="1">
+    <row r="85" ht="12.75" customHeight="1">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -11672,7 +11661,7 @@
       <c r="Y85" s="2"/>
       <c r="Z85" s="2"/>
     </row>
-    <row r="86" spans="1:26" ht="12.75" customHeight="1">
+    <row r="86" ht="12.75" customHeight="1">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -11700,7 +11689,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" spans="1:26" ht="12.75" customHeight="1">
+    <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -11728,7 +11717,7 @@
       <c r="Y87" s="2"/>
       <c r="Z87" s="2"/>
     </row>
-    <row r="88" spans="1:26" ht="12.75" customHeight="1">
+    <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -11756,7 +11745,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" spans="1:26" ht="12.75" customHeight="1">
+    <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -11784,7 +11773,7 @@
       <c r="Y89" s="2"/>
       <c r="Z89" s="2"/>
     </row>
-    <row r="90" spans="1:26" ht="12.75" customHeight="1">
+    <row r="90" ht="12.75" customHeight="1">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -11812,7 +11801,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" spans="1:26" ht="12.75" customHeight="1">
+    <row r="91" ht="12.75" customHeight="1">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -11840,7 +11829,7 @@
       <c r="Y91" s="2"/>
       <c r="Z91" s="2"/>
     </row>
-    <row r="92" spans="1:26" ht="12.75" customHeight="1">
+    <row r="92" ht="12.75" customHeight="1">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -11868,7 +11857,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" spans="1:26" ht="12.75" customHeight="1">
+    <row r="93" ht="12.75" customHeight="1">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -11896,7 +11885,7 @@
       <c r="Y93" s="2"/>
       <c r="Z93" s="2"/>
     </row>
-    <row r="94" spans="1:26" ht="12.75" customHeight="1">
+    <row r="94" ht="12.75" customHeight="1">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -11924,7 +11913,7 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" spans="1:26" ht="12.75" customHeight="1">
+    <row r="95" ht="12.75" customHeight="1">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -11952,7 +11941,7 @@
       <c r="Y95" s="2"/>
       <c r="Z95" s="2"/>
     </row>
-    <row r="96" spans="1:26" ht="12.75" customHeight="1">
+    <row r="96" ht="12.75" customHeight="1">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -11980,7 +11969,7 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" spans="1:26" ht="12.75" customHeight="1">
+    <row r="97" ht="12.75" customHeight="1">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -12008,7 +11997,7 @@
       <c r="Y97" s="2"/>
       <c r="Z97" s="2"/>
     </row>
-    <row r="98" spans="1:26" ht="12.75" customHeight="1">
+    <row r="98" ht="12.75" customHeight="1">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -12036,7 +12025,7 @@
       <c r="Y98" s="2"/>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" spans="1:26" ht="12.75" customHeight="1">
+    <row r="99" ht="12.75" customHeight="1">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -12064,7 +12053,7 @@
       <c r="Y99" s="2"/>
       <c r="Z99" s="2"/>
     </row>
-    <row r="100" spans="1:26" ht="12.75" customHeight="1">
+    <row r="100" ht="12.75" customHeight="1">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -12092,7 +12081,7 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" spans="1:26" ht="12.75" customHeight="1">
+    <row r="101" ht="12.75" customHeight="1">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -12120,7 +12109,7 @@
       <c r="Y101" s="2"/>
       <c r="Z101" s="2"/>
     </row>
-    <row r="102" spans="1:26" ht="12.75" customHeight="1">
+    <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -12148,7 +12137,7 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" spans="1:26" ht="12.75" customHeight="1">
+    <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -12176,7 +12165,7 @@
       <c r="Y103" s="2"/>
       <c r="Z103" s="2"/>
     </row>
-    <row r="104" spans="1:26" ht="12.75" customHeight="1">
+    <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -12204,7 +12193,7 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
-    <row r="105" spans="1:26" ht="12.75" customHeight="1">
+    <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -12232,7 +12221,7 @@
       <c r="Y105" s="2"/>
       <c r="Z105" s="2"/>
     </row>
-    <row r="106" spans="1:26" ht="12.75" customHeight="1">
+    <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -12260,7 +12249,7 @@
       <c r="Y106" s="2"/>
       <c r="Z106" s="2"/>
     </row>
-    <row r="107" spans="1:26" ht="12.75" customHeight="1">
+    <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -12288,7 +12277,7 @@
       <c r="Y107" s="2"/>
       <c r="Z107" s="2"/>
     </row>
-    <row r="108" spans="1:26" ht="12.75" customHeight="1">
+    <row r="108" ht="12.75" customHeight="1">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -12316,7 +12305,7 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" spans="1:26" ht="12.75" customHeight="1">
+    <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -12344,7 +12333,7 @@
       <c r="Y109" s="2"/>
       <c r="Z109" s="2"/>
     </row>
-    <row r="110" spans="1:26" ht="12.75" customHeight="1">
+    <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -12372,7 +12361,7 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
-    <row r="111" spans="1:26" ht="12.75" customHeight="1">
+    <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -12400,7 +12389,7 @@
       <c r="Y111" s="2"/>
       <c r="Z111" s="2"/>
     </row>
-    <row r="112" spans="1:26" ht="12.75" customHeight="1">
+    <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -12428,7 +12417,7 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
     </row>
-    <row r="113" spans="1:26" ht="12.75" customHeight="1">
+    <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -12456,7 +12445,7 @@
       <c r="Y113" s="2"/>
       <c r="Z113" s="2"/>
     </row>
-    <row r="114" spans="1:26" ht="12.75" customHeight="1">
+    <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -12484,7 +12473,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115" spans="1:26" ht="12.75" customHeight="1">
+    <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -12512,7 +12501,7 @@
       <c r="Y115" s="2"/>
       <c r="Z115" s="2"/>
     </row>
-    <row r="116" spans="1:26" ht="12.75" customHeight="1">
+    <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -12540,7 +12529,7 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117" spans="1:26" ht="12.75" customHeight="1">
+    <row r="117" ht="12.75" customHeight="1">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -12568,7 +12557,7 @@
       <c r="Y117" s="2"/>
       <c r="Z117" s="2"/>
     </row>
-    <row r="118" spans="1:26" ht="12.75" customHeight="1">
+    <row r="118" ht="12.75" customHeight="1">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -12596,7 +12585,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119" spans="1:26" ht="12.75" customHeight="1">
+    <row r="119" ht="12.75" customHeight="1">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -12624,7 +12613,7 @@
       <c r="Y119" s="2"/>
       <c r="Z119" s="2"/>
     </row>
-    <row r="120" spans="1:26" ht="12.75" customHeight="1">
+    <row r="120" ht="12.75" customHeight="1">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -12652,7 +12641,7 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121" spans="1:26" ht="12.75" customHeight="1">
+    <row r="121" ht="12.75" customHeight="1">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -12680,7 +12669,7 @@
       <c r="Y121" s="2"/>
       <c r="Z121" s="2"/>
     </row>
-    <row r="122" spans="1:26" ht="12.75" customHeight="1">
+    <row r="122" ht="12.75" customHeight="1">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -12708,7 +12697,7 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123" spans="1:26" ht="12.75" customHeight="1">
+    <row r="123" ht="12.75" customHeight="1">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -12736,7 +12725,7 @@
       <c r="Y123" s="2"/>
       <c r="Z123" s="2"/>
     </row>
-    <row r="124" spans="1:26" ht="12.75" customHeight="1">
+    <row r="124" ht="12.75" customHeight="1">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -12764,7 +12753,7 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125" spans="1:26" ht="12.75" customHeight="1">
+    <row r="125" ht="12.75" customHeight="1">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -12792,7 +12781,7 @@
       <c r="Y125" s="2"/>
       <c r="Z125" s="2"/>
     </row>
-    <row r="126" spans="1:26" ht="12.75" customHeight="1">
+    <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -12820,7 +12809,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127" spans="1:26" ht="12.75" customHeight="1">
+    <row r="127" ht="12.75" customHeight="1">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -12848,7 +12837,7 @@
       <c r="Y127" s="2"/>
       <c r="Z127" s="2"/>
     </row>
-    <row r="128" spans="1:26" ht="12.75" customHeight="1">
+    <row r="128" ht="12.75" customHeight="1">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -12876,7 +12865,7 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129" spans="1:26" ht="12.75" customHeight="1">
+    <row r="129" ht="12.75" customHeight="1">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -12904,7 +12893,7 @@
       <c r="Y129" s="2"/>
       <c r="Z129" s="2"/>
     </row>
-    <row r="130" spans="1:26" ht="12.75" customHeight="1">
+    <row r="130" ht="12.75" customHeight="1">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -12932,7 +12921,7 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
     </row>
-    <row r="131" spans="1:26" ht="12.75" customHeight="1">
+    <row r="131" ht="12.75" customHeight="1">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -12960,7 +12949,7 @@
       <c r="Y131" s="2"/>
       <c r="Z131" s="2"/>
     </row>
-    <row r="132" spans="1:26" ht="12.75" customHeight="1">
+    <row r="132" ht="12.75" customHeight="1">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -12988,7 +12977,7 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
     </row>
-    <row r="133" spans="1:26" ht="12.75" customHeight="1">
+    <row r="133" ht="12.75" customHeight="1">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -13016,7 +13005,7 @@
       <c r="Y133" s="2"/>
       <c r="Z133" s="2"/>
     </row>
-    <row r="134" spans="1:26" ht="12.75" customHeight="1">
+    <row r="134" ht="12.75" customHeight="1">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -13044,7 +13033,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" spans="1:26" ht="12.75" customHeight="1">
+    <row r="135" ht="12.75" customHeight="1">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -13072,7 +13061,7 @@
       <c r="Y135" s="2"/>
       <c r="Z135" s="2"/>
     </row>
-    <row r="136" spans="1:26" ht="12.75" customHeight="1">
+    <row r="136" ht="12.75" customHeight="1">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -13100,7 +13089,7 @@
       <c r="Y136" s="2"/>
       <c r="Z136" s="2"/>
     </row>
-    <row r="137" spans="1:26" ht="12.75" customHeight="1">
+    <row r="137" ht="12.75" customHeight="1">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -13128,7 +13117,7 @@
       <c r="Y137" s="2"/>
       <c r="Z137" s="2"/>
     </row>
-    <row r="138" spans="1:26" ht="12.75" customHeight="1">
+    <row r="138" ht="12.75" customHeight="1">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -13156,7 +13145,7 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
     </row>
-    <row r="139" spans="1:26" ht="12.75" customHeight="1">
+    <row r="139" ht="12.75" customHeight="1">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -13184,7 +13173,7 @@
       <c r="Y139" s="2"/>
       <c r="Z139" s="2"/>
     </row>
-    <row r="140" spans="1:26" ht="12.75" customHeight="1">
+    <row r="140" ht="12.75" customHeight="1">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -13212,7 +13201,7 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
     </row>
-    <row r="141" spans="1:26" ht="12.75" customHeight="1">
+    <row r="141" ht="12.75" customHeight="1">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -13240,7 +13229,7 @@
       <c r="Y141" s="2"/>
       <c r="Z141" s="2"/>
     </row>
-    <row r="142" spans="1:26" ht="12.75" customHeight="1">
+    <row r="142" ht="12.75" customHeight="1">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -13268,7 +13257,7 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
     </row>
-    <row r="143" spans="1:26" ht="12.75" customHeight="1">
+    <row r="143" ht="12.75" customHeight="1">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -13296,7 +13285,7 @@
       <c r="Y143" s="2"/>
       <c r="Z143" s="2"/>
     </row>
-    <row r="144" spans="1:26" ht="12.75" customHeight="1">
+    <row r="144" ht="12.75" customHeight="1">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -13324,7 +13313,7 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
     </row>
-    <row r="145" spans="1:26" ht="12.75" customHeight="1">
+    <row r="145" ht="12.75" customHeight="1">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -13352,7 +13341,7 @@
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
     </row>
-    <row r="146" spans="1:26" ht="12.75" customHeight="1">
+    <row r="146" ht="12.75" customHeight="1">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -13380,7 +13369,7 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147" spans="1:26" ht="12.75" customHeight="1">
+    <row r="147" ht="12.75" customHeight="1">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -13408,7 +13397,7 @@
       <c r="Y147" s="2"/>
       <c r="Z147" s="2"/>
     </row>
-    <row r="148" spans="1:26" ht="12.75" customHeight="1">
+    <row r="148" ht="12.75" customHeight="1">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -13436,7 +13425,7 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149" spans="1:26" ht="12.75" customHeight="1">
+    <row r="149" ht="12.75" customHeight="1">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -13464,7 +13453,7 @@
       <c r="Y149" s="2"/>
       <c r="Z149" s="2"/>
     </row>
-    <row r="150" spans="1:26" ht="12.75" customHeight="1">
+    <row r="150" ht="12.75" customHeight="1">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -13492,7 +13481,7 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
     </row>
-    <row r="151" spans="1:26" ht="12.75" customHeight="1">
+    <row r="151" ht="12.75" customHeight="1">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -13520,7 +13509,7 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152" spans="1:26" ht="12.75" customHeight="1">
+    <row r="152" ht="12.75" customHeight="1">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -13548,7 +13537,7 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
     </row>
-    <row r="153" spans="1:26" ht="12.75" customHeight="1">
+    <row r="153" ht="12.75" customHeight="1">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -13576,7 +13565,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154" spans="1:26" ht="12.75" customHeight="1">
+    <row r="154" ht="12.75" customHeight="1">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -13604,7 +13593,7 @@
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
     </row>
-    <row r="155" spans="1:26" ht="12.75" customHeight="1">
+    <row r="155" ht="12.75" customHeight="1">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -13632,7 +13621,7 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
     </row>
-    <row r="156" spans="1:26" ht="12.75" customHeight="1">
+    <row r="156" ht="12.75" customHeight="1">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -13660,7 +13649,7 @@
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
     </row>
-    <row r="157" spans="1:26" ht="12.75" customHeight="1">
+    <row r="157" ht="12.75" customHeight="1">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -13688,7 +13677,7 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158" spans="1:26" ht="12.75" customHeight="1">
+    <row r="158" ht="12.75" customHeight="1">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -13716,7 +13705,7 @@
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
     </row>
-    <row r="159" spans="1:26" ht="12.75" customHeight="1">
+    <row r="159" ht="12.75" customHeight="1">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -13744,7 +13733,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160" spans="1:26" ht="12.75" customHeight="1">
+    <row r="160" ht="12.75" customHeight="1">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -13772,7 +13761,7 @@
       <c r="Y160" s="2"/>
       <c r="Z160" s="2"/>
     </row>
-    <row r="161" spans="1:26" ht="12.75" customHeight="1">
+    <row r="161" ht="12.75" customHeight="1">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -13800,7 +13789,7 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
     </row>
-    <row r="162" spans="1:26" ht="12.75" customHeight="1">
+    <row r="162" ht="12.75" customHeight="1">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -13828,7 +13817,7 @@
       <c r="Y162" s="2"/>
       <c r="Z162" s="2"/>
     </row>
-    <row r="163" spans="1:26" ht="12.75" customHeight="1">
+    <row r="163" ht="12.75" customHeight="1">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -13856,7 +13845,7 @@
       <c r="Y163" s="2"/>
       <c r="Z163" s="2"/>
     </row>
-    <row r="164" spans="1:26" ht="12.75" customHeight="1">
+    <row r="164" ht="12.75" customHeight="1">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -13884,7 +13873,7 @@
       <c r="Y164" s="2"/>
       <c r="Z164" s="2"/>
     </row>
-    <row r="165" spans="1:26" ht="12.75" customHeight="1">
+    <row r="165" ht="12.75" customHeight="1">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -13912,7 +13901,7 @@
       <c r="Y165" s="2"/>
       <c r="Z165" s="2"/>
     </row>
-    <row r="166" spans="1:26" ht="12.75" customHeight="1">
+    <row r="166" ht="12.75" customHeight="1">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -13940,7 +13929,7 @@
       <c r="Y166" s="2"/>
       <c r="Z166" s="2"/>
     </row>
-    <row r="167" spans="1:26" ht="12.75" customHeight="1">
+    <row r="167" ht="12.75" customHeight="1">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -13968,7 +13957,7 @@
       <c r="Y167" s="2"/>
       <c r="Z167" s="2"/>
     </row>
-    <row r="168" spans="1:26" ht="12.75" customHeight="1">
+    <row r="168" ht="12.75" customHeight="1">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -13996,7 +13985,7 @@
       <c r="Y168" s="2"/>
       <c r="Z168" s="2"/>
     </row>
-    <row r="169" spans="1:26" ht="12.75" customHeight="1">
+    <row r="169" ht="12.75" customHeight="1">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -14024,7 +14013,7 @@
       <c r="Y169" s="2"/>
       <c r="Z169" s="2"/>
     </row>
-    <row r="170" spans="1:26" ht="12.75" customHeight="1">
+    <row r="170" ht="12.75" customHeight="1">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -14052,7 +14041,7 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
     </row>
-    <row r="171" spans="1:26" ht="12.75" customHeight="1">
+    <row r="171" ht="12.75" customHeight="1">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -14080,7 +14069,7 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
     </row>
-    <row r="172" spans="1:26" ht="12.75" customHeight="1">
+    <row r="172" ht="12.75" customHeight="1">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -14108,7 +14097,7 @@
       <c r="Y172" s="2"/>
       <c r="Z172" s="2"/>
     </row>
-    <row r="173" spans="1:26" ht="12.75" customHeight="1">
+    <row r="173" ht="12.75" customHeight="1">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -14136,7 +14125,7 @@
       <c r="Y173" s="2"/>
       <c r="Z173" s="2"/>
     </row>
-    <row r="174" spans="1:26" ht="12.75" customHeight="1">
+    <row r="174" ht="12.75" customHeight="1">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -14164,7 +14153,7 @@
       <c r="Y174" s="2"/>
       <c r="Z174" s="2"/>
     </row>
-    <row r="175" spans="1:26" ht="12.75" customHeight="1">
+    <row r="175" ht="12.75" customHeight="1">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -14192,7 +14181,7 @@
       <c r="Y175" s="2"/>
       <c r="Z175" s="2"/>
     </row>
-    <row r="176" spans="1:26" ht="12.75" customHeight="1">
+    <row r="176" ht="12.75" customHeight="1">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -14220,7 +14209,7 @@
       <c r="Y176" s="2"/>
       <c r="Z176" s="2"/>
     </row>
-    <row r="177" spans="1:26" ht="12.75" customHeight="1">
+    <row r="177" ht="12.75" customHeight="1">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -14248,7 +14237,7 @@
       <c r="Y177" s="2"/>
       <c r="Z177" s="2"/>
     </row>
-    <row r="178" spans="1:26" ht="12.75" customHeight="1">
+    <row r="178" ht="12.75" customHeight="1">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -14276,7 +14265,7 @@
       <c r="Y178" s="2"/>
       <c r="Z178" s="2"/>
     </row>
-    <row r="179" spans="1:26" ht="12.75" customHeight="1">
+    <row r="179" ht="12.75" customHeight="1">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -14304,7 +14293,7 @@
       <c r="Y179" s="2"/>
       <c r="Z179" s="2"/>
     </row>
-    <row r="180" spans="1:26" ht="12.75" customHeight="1">
+    <row r="180" ht="12.75" customHeight="1">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -14332,7 +14321,7 @@
       <c r="Y180" s="2"/>
       <c r="Z180" s="2"/>
     </row>
-    <row r="181" spans="1:26" ht="12.75" customHeight="1">
+    <row r="181" ht="12.75" customHeight="1">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -14360,7 +14349,7 @@
       <c r="Y181" s="2"/>
       <c r="Z181" s="2"/>
     </row>
-    <row r="182" spans="1:26" ht="12.75" customHeight="1">
+    <row r="182" ht="12.75" customHeight="1">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -14388,7 +14377,7 @@
       <c r="Y182" s="2"/>
       <c r="Z182" s="2"/>
     </row>
-    <row r="183" spans="1:26" ht="12.75" customHeight="1">
+    <row r="183" ht="12.75" customHeight="1">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -14416,7 +14405,7 @@
       <c r="Y183" s="2"/>
       <c r="Z183" s="2"/>
     </row>
-    <row r="184" spans="1:26" ht="12.75" customHeight="1">
+    <row r="184" ht="12.75" customHeight="1">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -14444,7 +14433,7 @@
       <c r="Y184" s="2"/>
       <c r="Z184" s="2"/>
     </row>
-    <row r="185" spans="1:26" ht="12.75" customHeight="1">
+    <row r="185" ht="12.75" customHeight="1">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -14472,7 +14461,7 @@
       <c r="Y185" s="2"/>
       <c r="Z185" s="2"/>
     </row>
-    <row r="186" spans="1:26" ht="12.75" customHeight="1">
+    <row r="186" ht="12.75" customHeight="1">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -14500,7 +14489,7 @@
       <c r="Y186" s="2"/>
       <c r="Z186" s="2"/>
     </row>
-    <row r="187" spans="1:26" ht="12.75" customHeight="1">
+    <row r="187" ht="12.75" customHeight="1">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -14528,7 +14517,7 @@
       <c r="Y187" s="2"/>
       <c r="Z187" s="2"/>
     </row>
-    <row r="188" spans="1:26" ht="12.75" customHeight="1">
+    <row r="188" ht="12.75" customHeight="1">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -14556,7 +14545,7 @@
       <c r="Y188" s="2"/>
       <c r="Z188" s="2"/>
     </row>
-    <row r="189" spans="1:26" ht="12.75" customHeight="1">
+    <row r="189" ht="12.75" customHeight="1">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -14584,7 +14573,7 @@
       <c r="Y189" s="2"/>
       <c r="Z189" s="2"/>
     </row>
-    <row r="190" spans="1:26" ht="12.75" customHeight="1">
+    <row r="190" ht="12.75" customHeight="1">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -14612,7 +14601,7 @@
       <c r="Y190" s="2"/>
       <c r="Z190" s="2"/>
     </row>
-    <row r="191" spans="1:26" ht="12.75" customHeight="1">
+    <row r="191" ht="12.75" customHeight="1">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -14640,7 +14629,7 @@
       <c r="Y191" s="2"/>
       <c r="Z191" s="2"/>
     </row>
-    <row r="192" spans="1:26" ht="12.75" customHeight="1">
+    <row r="192" ht="12.75" customHeight="1">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -14668,7 +14657,7 @@
       <c r="Y192" s="2"/>
       <c r="Z192" s="2"/>
     </row>
-    <row r="193" spans="1:26" ht="12.75" customHeight="1">
+    <row r="193" ht="12.75" customHeight="1">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -14696,7 +14685,7 @@
       <c r="Y193" s="2"/>
       <c r="Z193" s="2"/>
     </row>
-    <row r="194" spans="1:26" ht="12.75" customHeight="1">
+    <row r="194" ht="12.75" customHeight="1">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -14724,7 +14713,7 @@
       <c r="Y194" s="2"/>
       <c r="Z194" s="2"/>
     </row>
-    <row r="195" spans="1:26" ht="12.75" customHeight="1">
+    <row r="195" ht="12.75" customHeight="1">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -14752,7 +14741,7 @@
       <c r="Y195" s="2"/>
       <c r="Z195" s="2"/>
     </row>
-    <row r="196" spans="1:26" ht="12.75" customHeight="1">
+    <row r="196" ht="12.75" customHeight="1">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -14780,7 +14769,7 @@
       <c r="Y196" s="2"/>
       <c r="Z196" s="2"/>
     </row>
-    <row r="197" spans="1:26" ht="12.75" customHeight="1">
+    <row r="197" ht="12.75" customHeight="1">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -14808,7 +14797,7 @@
       <c r="Y197" s="2"/>
       <c r="Z197" s="2"/>
     </row>
-    <row r="198" spans="1:26" ht="12.75" customHeight="1">
+    <row r="198" ht="12.75" customHeight="1">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -14836,7 +14825,7 @@
       <c r="Y198" s="2"/>
       <c r="Z198" s="2"/>
     </row>
-    <row r="199" spans="1:26" ht="12.75" customHeight="1">
+    <row r="199" ht="12.75" customHeight="1">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -14864,7 +14853,7 @@
       <c r="Y199" s="2"/>
       <c r="Z199" s="2"/>
     </row>
-    <row r="200" spans="1:26" ht="12.75" customHeight="1">
+    <row r="200" ht="12.75" customHeight="1">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -14892,7 +14881,7 @@
       <c r="Y200" s="2"/>
       <c r="Z200" s="2"/>
     </row>
-    <row r="201" spans="1:26" ht="12.75" customHeight="1">
+    <row r="201" ht="12.75" customHeight="1">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -14920,7 +14909,7 @@
       <c r="Y201" s="2"/>
       <c r="Z201" s="2"/>
     </row>
-    <row r="202" spans="1:26" ht="12.75" customHeight="1">
+    <row r="202" ht="12.75" customHeight="1">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -14948,7 +14937,7 @@
       <c r="Y202" s="2"/>
       <c r="Z202" s="2"/>
     </row>
-    <row r="203" spans="1:26" ht="12.75" customHeight="1">
+    <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -14976,7 +14965,7 @@
       <c r="Y203" s="2"/>
       <c r="Z203" s="2"/>
     </row>
-    <row r="204" spans="1:26" ht="12.75" customHeight="1">
+    <row r="204" ht="12.75" customHeight="1">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -15004,7 +14993,7 @@
       <c r="Y204" s="2"/>
       <c r="Z204" s="2"/>
     </row>
-    <row r="205" spans="1:26" ht="12.75" customHeight="1">
+    <row r="205" ht="12.75" customHeight="1">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -15032,7 +15021,7 @@
       <c r="Y205" s="2"/>
       <c r="Z205" s="2"/>
     </row>
-    <row r="206" spans="1:26" ht="12.75" customHeight="1">
+    <row r="206" ht="12.75" customHeight="1">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -15060,7 +15049,7 @@
       <c r="Y206" s="2"/>
       <c r="Z206" s="2"/>
     </row>
-    <row r="207" spans="1:26" ht="12.75" customHeight="1">
+    <row r="207" ht="12.75" customHeight="1">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -15088,7 +15077,7 @@
       <c r="Y207" s="2"/>
       <c r="Z207" s="2"/>
     </row>
-    <row r="208" spans="1:26" ht="12.75" customHeight="1">
+    <row r="208" ht="12.75" customHeight="1">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -15116,7 +15105,7 @@
       <c r="Y208" s="2"/>
       <c r="Z208" s="2"/>
     </row>
-    <row r="209" spans="1:26" ht="12.75" customHeight="1">
+    <row r="209" ht="12.75" customHeight="1">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -15144,7 +15133,7 @@
       <c r="Y209" s="2"/>
       <c r="Z209" s="2"/>
     </row>
-    <row r="210" spans="1:26" ht="12.75" customHeight="1">
+    <row r="210" ht="12.75" customHeight="1">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -15172,7 +15161,7 @@
       <c r="Y210" s="2"/>
       <c r="Z210" s="2"/>
     </row>
-    <row r="211" spans="1:26" ht="12.75" customHeight="1">
+    <row r="211" ht="12.75" customHeight="1">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -15200,7 +15189,7 @@
       <c r="Y211" s="2"/>
       <c r="Z211" s="2"/>
     </row>
-    <row r="212" spans="1:26" ht="12.75" customHeight="1">
+    <row r="212" ht="12.75" customHeight="1">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -15228,7 +15217,7 @@
       <c r="Y212" s="2"/>
       <c r="Z212" s="2"/>
     </row>
-    <row r="213" spans="1:26" ht="12.75" customHeight="1">
+    <row r="213" ht="12.75" customHeight="1">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -15256,7 +15245,7 @@
       <c r="Y213" s="2"/>
       <c r="Z213" s="2"/>
     </row>
-    <row r="214" spans="1:26" ht="12.75" customHeight="1">
+    <row r="214" ht="12.75" customHeight="1">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -15284,7 +15273,7 @@
       <c r="Y214" s="2"/>
       <c r="Z214" s="2"/>
     </row>
-    <row r="215" spans="1:26" ht="12.75" customHeight="1">
+    <row r="215" ht="12.75" customHeight="1">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -15312,7 +15301,7 @@
       <c r="Y215" s="2"/>
       <c r="Z215" s="2"/>
     </row>
-    <row r="216" spans="1:26" ht="12.75" customHeight="1">
+    <row r="216" ht="12.75" customHeight="1">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -15340,7 +15329,7 @@
       <c r="Y216" s="2"/>
       <c r="Z216" s="2"/>
     </row>
-    <row r="217" spans="1:26" ht="12.75" customHeight="1">
+    <row r="217" ht="12.75" customHeight="1">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -15368,7 +15357,7 @@
       <c r="Y217" s="2"/>
       <c r="Z217" s="2"/>
     </row>
-    <row r="218" spans="1:26" ht="12.75" customHeight="1">
+    <row r="218" ht="12.75" customHeight="1">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -15396,7 +15385,7 @@
       <c r="Y218" s="2"/>
       <c r="Z218" s="2"/>
     </row>
-    <row r="219" spans="1:26" ht="12.75" customHeight="1">
+    <row r="219" ht="12.75" customHeight="1">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -15424,7 +15413,7 @@
       <c r="Y219" s="2"/>
       <c r="Z219" s="2"/>
     </row>
-    <row r="220" spans="1:26" ht="12.75" customHeight="1">
+    <row r="220" ht="12.75" customHeight="1">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -15452,10 +15441,10 @@
       <c r="Y220" s="2"/>
       <c r="Z220" s="2"/>
     </row>
-    <row r="221" spans="1:26" ht="12.75" customHeight="1"/>
-    <row r="222" spans="1:26" ht="12.75" customHeight="1"/>
-    <row r="223" spans="1:26" ht="12.75" customHeight="1"/>
-    <row r="224" spans="1:26" ht="12.75" customHeight="1"/>
+    <row r="221" ht="12.75" customHeight="1"/>
+    <row r="222" ht="12.75" customHeight="1"/>
+    <row r="223" ht="12.75" customHeight="1"/>
+    <row r="224" ht="12.75" customHeight="1"/>
     <row r="225" ht="12.75" customHeight="1"/>
     <row r="226" ht="12.75" customHeight="1"/>
     <row r="227" ht="12.75" customHeight="1"/>
@@ -16233,7 +16222,9 @@
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>